--- a/XLS-002 - Risk Register - v0.2.xlsx
+++ b/XLS-002 - Risk Register - v0.2.xlsx
@@ -496,7 +496,7 @@
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>PMOC Software | Fase 1 | v0.2 DRAFT | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved | Status: aguardando segunda revisão formal da Services.NET | Score = Probabilidade x Impacto (escala 1 a 5).</t>
+          <t>PMOC Software | Fase 1 | v0.2 — APPROVED | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved; Services.NET segunda revisão formal da Fase 1 v0.2 | Status: APPROVED WITH OPEN ACTIONS — Fase 1 aprovada formalmente pela Services.NET em 22/09/2026; Fase 2 não iniciada | Score = Probabilidade x Impacto (escala 1 a 5).</t>
         </is>
       </c>
     </row>
@@ -747,17 +747,17 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Ausência de cliente-piloto engajado leva a requisitos presumidos</t>
+          <t>Interlocutores, disponibilidade, compromisso operacional ou agenda do tenant-piloto Clima Zero Climatização não se formalizarem a tempo</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Produto desalinhado da operação real</t>
+          <t>Levantamento e validação do MVP atrasados; risco de requisitos presumidos</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Product Owner (STK-002)</t>
+          <t>Product Owner institucional (STK-002) + Clima Zero Climatização (STK-010)</t>
         </is>
       </c>
       <c r="F8" s="16" t="n">
@@ -777,7 +777,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Confirmar piloto antes da Fase 2; registrar tudo não confirmado como hipótese</t>
+          <t>Tenant-piloto definido; registrar interlocutores, disponibilidade e agenda em OQ-022/DEP-004 antes de avançar operacionalmente</t>
         </is>
       </c>
       <c r="K8" s="16" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="L8" s="16" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2 — identidade do tenant definida; risco operacional mantido</t>
         </is>
       </c>
     </row>
@@ -1691,6 +1691,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="10">
       <c r="A4" s="18" t="inlineStr">
         <is>
